--- a/liaisons_Super_Constellation/Reseau_United_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_United_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Transcontinental (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Lignes DC-6" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,7 +604,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ATTENTION : United Air Lines était une grande cliente Douglas (DC-6/DC-7 « Mainliner ») et n'a PAS exploité le L-1049. Feuillet illustratif, ENTIÈREMENT RECONSTITUÉ [R].</v>
+        <v>Sources : United Air Lines a exploité de nombreux Douglas DC-6 « Mainliner » sur ses lignes transcontinentales et de la côte Ouest.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -633,7 +633,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[S] Sourcé : uniquement les corridors réels du réseau United — pas l'appareil.</v>
+        <v>Ligne exploitée historiquement en Douglas DC-6 ; proposée ici pour le Super Constellation L-1049, appareil de même catégorie (quadrimoteur à pistons long-courrier).</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -662,7 +662,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -691,36 +691,65 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
   </ignoredErrors>
 </worksheet>
 </file>